--- a/output/detection/temporal=false-retriever=sentence-transformers-all-mpnet-base-v2-search=hybrid-rerank=cross-encoder-ms-marco-minilm-l-6-v2-summarizer=false/results.xlsx
+++ b/output/detection/temporal=false-retriever=sentence-transformers-all-mpnet-base-v2-search=hybrid-rerank=cross-encoder-ms-marco-minilm-l-6-v2-summarizer=false/results.xlsx
@@ -413,196 +413,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>temporal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>retriever</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>search</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rerank</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>summarizer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>configuration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>predict_f1_macro</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>predict_accuracy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="b">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>output/detection/temporal=false-retriever=sentence-transformers-all-mpnet-base-v2-search=hybrid-rerank=cross-encoder-ms-marco-minilm-l-6-v2-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>sentence-transformers-all-mpnet-base-v2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>cross-encoder-ms-marco-minilm-l-6-v2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>ModernBERT-base</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>bs16_lr3e-5_ep5</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.745711260809684</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.746177370030581</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="b">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output/detection/temporal=false-retriever=sentence-transformers-all-mpnet-base-v2-search=hybrid-rerank=cross-encoder-ms-marco-minilm-l-6-v2-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>sentence-transformers-all-mpnet-base-v2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>cross-encoder-ms-marco-minilm-l-6-v2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>longformer-base-4096</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>bs16_lr3e-5_ep5</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.7825818232897879</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.7828746177370031</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="b">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>output/detection/temporal=false-retriever=sentence-transformers-all-mpnet-base-v2-search=hybrid-rerank=cross-encoder-ms-marco-minilm-l-6-v2-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
         <v>0</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>sentence-transformers-all-mpnet-base-v2</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>cross-encoder-ms-marco-minilm-l-6-v2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>roberta-base</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>bs16_lr5e-5_ep3</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.7704275056398544</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.7706422018348624</v>
       </c>
     </row>
